--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-birth-record-identifier-child.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-birth-record-identifier-child.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-09T11:35:05-04:00</t>
+    <t>2025-08-11T15:01:09-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Birth Record Identifier (Observation). For use in Maternal Death. This includes the record identifier, the jurisdiction, and the birth year of a child.
+    <t>Birth Record Identifier (Observation). For use in Maternal Death. This includes the record identifier, the jurisdiction, and the birth year of a child.
 The subject is implicitly the Decedent (mother), whose death was related to the to the birth referenced by the identifier.</t>
   </si>
   <si>
@@ -1917,17 +1917,17 @@
   <dimension ref="A1:AP87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.5390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.8984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="92.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="100.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1936,28 +1936,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="53.24609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.3046875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="16.2578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="70.50390625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-birth-record-identifier-child.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-birth-record-identifier-child.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-11T15:01:09-04:00</t>
+    <t>2025-11-25T14:04:25-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -378,7 +378,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -514,7 +514,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -543,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -629,7 +629,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -671,7 +671,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -695,7 +695,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -749,7 +749,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -840,7 +840,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -925,7 +925,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -957,7 +957,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1013,7 +1013,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1046,7 +1046,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1058,7 +1058,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1086,7 +1086,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1184,7 +1184,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1234,7 +1234,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1267,7 +1267,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1304,7 +1304,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1326,7 +1326,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1927,7 +1927,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="100.1171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/docs/v3.0.0-preview1/StructureDefinition-VRM-birth-record-identifier-child.xlsx
+++ b/docs/v3.0.0-preview1/StructureDefinition-VRM-birth-record-identifier-child.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-25T14:04:25-05:00</t>
+    <t>2026-03-24T12:23:49-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -378,7 +378,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -514,7 +514,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -543,7 +543,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -629,7 +629,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -671,7 +671,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -695,7 +695,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Location|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Group|Device|Location)
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -749,7 +749,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1)
+    <t xml:space="preserve">Reference(Encounter)
 </t>
   </si>
   <si>
@@ -840,7 +840,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -925,7 +925,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -957,7 +957,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1013,7 +1013,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1046,7 +1046,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1058,7 +1058,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1086,7 +1086,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1184,7 +1184,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1234,7 +1234,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1267,7 +1267,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1304,7 +1304,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1326,7 +1326,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
 </t>
   </si>
   <si>
@@ -1927,7 +1927,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="100.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
